--- a/config/auto_configs/2023_Hyundai_Hyundai_IONIQ 5(NE EV)_70kW+160kW.xlsx
+++ b/config/auto_configs/2023_Hyundai_Hyundai_IONIQ 5(NE EV)_70kW+160kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B132600</t>
+          <t>C110913</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B132700</t>
+          <t>C120001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B132800</t>
+          <t>C120102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,17 +586,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B132900</t>
+          <t>C120202</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B133000</t>
+          <t>C120301</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B133100</t>
+          <t>C120402</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,17 +652,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B133200</t>
+          <t>C120502</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -674,17 +674,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B133300</t>
+          <t>C120601</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -696,17 +696,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B133400</t>
+          <t>C120702</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -718,17 +718,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B133500</t>
+          <t>C120802</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -740,17 +740,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B134600</t>
+          <t>C120901</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B134700</t>
+          <t>C121002</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,17 +784,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B134800</t>
+          <t>C121102</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -806,17 +806,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B134900</t>
+          <t>C123501</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -828,17 +828,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B135200</t>
+          <t>C135801</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B135300</t>
+          <t>C137801</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -872,17 +872,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B135400</t>
+          <t>C150301</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -894,17 +894,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B135500</t>
+          <t>C161C86</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -916,17 +916,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B136100</t>
+          <t>C165A87</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -938,17 +938,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B136200</t>
+          <t>C166982</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -960,17 +960,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B136300</t>
+          <t>C166983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -982,17 +982,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B136400</t>
+          <t>C182586</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1004,17 +1004,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B136700</t>
+          <t>C183986</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1026,17 +1026,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B136800</t>
+          <t>C184787</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1048,17 +1048,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B136900</t>
+          <t>C220277</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1070,17 +1070,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B137000</t>
+          <t>C222071</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1092,17 +1092,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B137800</t>
+          <t>C222074</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1114,17 +1114,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B137900</t>
+          <t>C222077</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B138000</t>
+          <t>C222094</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1158,17 +1158,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B138100</t>
+          <t>C222471</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1180,17 +1180,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B138200</t>
+          <t>C222474</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1202,17 +1202,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B138300</t>
+          <t>C222477</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1224,17 +1224,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B138400</t>
+          <t>C222494</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1246,17 +1246,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B138500</t>
+          <t>C238001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1268,17 +1268,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B140000</t>
+          <t>C240201</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1290,17 +1290,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B140100</t>
+          <t>C241611</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1312,17 +1312,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B140200</t>
+          <t>C241612</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1334,17 +1334,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B140300</t>
+          <t>C241613</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1356,17 +1356,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B140400</t>
+          <t>C241711</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1378,17 +1378,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B140500</t>
+          <t>C241712</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1400,17 +1400,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HMA_HK_01318</t>
+          <t>HMA_HK_01317</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B140900</t>
+          <t>C241713</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B141000</t>
+          <t>B132600</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B141200</t>
+          <t>B132700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B141300</t>
+          <t>B132800</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B141400</t>
+          <t>B132900</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B141500</t>
+          <t>B133000</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B141600</t>
+          <t>B133100</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B141700</t>
+          <t>B133200</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B141800</t>
+          <t>B133300</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B141900</t>
+          <t>B133400</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B145100</t>
+          <t>B133500</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B145200</t>
+          <t>B134600</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B145400</t>
+          <t>B134700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B145500</t>
+          <t>B134800</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B147300</t>
+          <t>B134900</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B147400</t>
+          <t>B135200</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B147500</t>
+          <t>B135300</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B147600</t>
+          <t>B135400</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B147700</t>
+          <t>B135500</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B147800</t>
+          <t>B136100</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B147900</t>
+          <t>B136200</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B148000</t>
+          <t>B136300</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B148100</t>
+          <t>B136400</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B148200</t>
+          <t>B136700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B148300</t>
+          <t>B136800</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B148400</t>
+          <t>B136900</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B148500</t>
+          <t>B137000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B148600</t>
+          <t>B137800</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B148700</t>
+          <t>B137900</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B148800</t>
+          <t>B138000</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B149000</t>
+          <t>B138100</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B149300</t>
+          <t>B138200</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B149400</t>
+          <t>B138300</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B151100</t>
+          <t>B138400</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B151200</t>
+          <t>B138500</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B151300</t>
+          <t>B140000</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B151400</t>
+          <t>B140100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B151500</t>
+          <t>B140200</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B151600</t>
+          <t>B140300</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B162000</t>
+          <t>B140400</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B165000</t>
+          <t>B140500</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B165100</t>
+          <t>B140900</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B165200</t>
+          <t>B141000</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B165800</t>
+          <t>B141200</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B167000</t>
+          <t>B141300</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B167600</t>
+          <t>B141400</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B167700</t>
+          <t>B141500</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B167800</t>
+          <t>B141600</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B168400</t>
+          <t>B141700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B173800</t>
+          <t>B141800</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B173900</t>
+          <t>B141900</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B174000</t>
+          <t>B145100</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B174100</t>
+          <t>B145200</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B174200</t>
+          <t>B145400</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B174400</t>
+          <t>B145500</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B174500</t>
+          <t>B147300</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B174600</t>
+          <t>B147400</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B174700</t>
+          <t>B147500</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B174800</t>
+          <t>B147600</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B176200</t>
+          <t>B147700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B250200</t>
+          <t>B147800</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B261300</t>
+          <t>B147900</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B261500</t>
+          <t>B148000</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B261600</t>
+          <t>B148100</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2808,17 +2808,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>C110913</t>
+          <t>B148200</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2830,17 +2830,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>C120001</t>
+          <t>B148300</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2852,17 +2852,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>C120102</t>
+          <t>B148400</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2874,17 +2874,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>C120202</t>
+          <t>B148500</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2896,17 +2896,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>C120301</t>
+          <t>B148600</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2918,17 +2918,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>C120402</t>
+          <t>B148700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2940,17 +2940,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>C120502</t>
+          <t>B148800</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2962,17 +2962,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>C120601</t>
+          <t>B149000</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2984,17 +2984,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>C120702</t>
+          <t>B149300</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3006,17 +3006,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>C120802</t>
+          <t>B149400</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3028,17 +3028,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>C120901</t>
+          <t>B151100</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3050,17 +3050,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>C121002</t>
+          <t>B151200</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3072,17 +3072,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>C121102</t>
+          <t>B151300</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3094,17 +3094,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>C123501</t>
+          <t>B151400</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3116,17 +3116,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>C135801</t>
+          <t>B151500</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3138,17 +3138,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>C137801</t>
+          <t>B151600</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3160,17 +3160,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>C150301</t>
+          <t>B162000</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3182,17 +3182,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>C161C86</t>
+          <t>B165000</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3204,17 +3204,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>C165A87</t>
+          <t>B165100</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3226,17 +3226,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>C166982</t>
+          <t>B165200</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3248,17 +3248,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>C166983</t>
+          <t>B165800</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3270,17 +3270,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>C182586</t>
+          <t>B167000</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3292,17 +3292,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>C183986</t>
+          <t>B167600</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3314,17 +3314,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>C184787</t>
+          <t>B167700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3336,17 +3336,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>C220277</t>
+          <t>B167800</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3358,17 +3358,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>C222071</t>
+          <t>B168400</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3380,17 +3380,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>C222074</t>
+          <t>B173800</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3402,17 +3402,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>C222077</t>
+          <t>B173900</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3424,17 +3424,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>C222094</t>
+          <t>B174000</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3446,17 +3446,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>C222471</t>
+          <t>B174100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3468,17 +3468,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>C222474</t>
+          <t>B174200</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3490,17 +3490,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>C222477</t>
+          <t>B174400</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3512,17 +3512,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>C222494</t>
+          <t>B174500</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3534,17 +3534,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>C238001</t>
+          <t>B174600</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3556,17 +3556,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>C240201</t>
+          <t>B174700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3578,17 +3578,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>C241611</t>
+          <t>B174800</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3600,17 +3600,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>C241612</t>
+          <t>B176200</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3622,17 +3622,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>C241613</t>
+          <t>B250200</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3644,17 +3644,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>C241711</t>
+          <t>B261300</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3666,17 +3666,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>C241712</t>
+          <t>B261500</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3688,20 +3688,1076 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HMA_HK_01317</t>
+          <t>HMA_HK_01318</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>C241713</t>
+          <t>B261600</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>HMA_HK_01320</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>HMA_HK_01321</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ADAS_D</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HMA_HK_01322</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>HMA_HK_01323</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AFCU</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HMA_HK_01324</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>HMA_HK_01325</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>APSM</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HMA_HK_01326</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>HMA_HK_01327</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>HMA_HK_01328</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>HMA_HK_01329</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HMA_HK_01330</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>HMA_HK_01331</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>DAU</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HMA_HK_01332</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>DSM-L</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>HMA_HK_01333</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>DSM-R</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HMA_HK_01334</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>HMA_HK_01335</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>HMA_HK_01336</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>HMA_HK_01337</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HMA_HK_01338</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>HMA_HK_01339</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>HMA_HK_01340</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>HMA_HK_01341</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>IBU-IMM</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HMA_HK_01342</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>HMA_HK_01343</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ICCU</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>HMA_HK_01344</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>HMA_HK_01345</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MCU-F</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>HMA_HK_01346</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MCU-R</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>HMA_HK_01347</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MFS</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>HMA_HK_01348</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HMA_HK_01349</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HMA_HK_01350</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PCM</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HMA_HK_01351</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>HMA_HK_01352</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PSM-RL</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>HMA_HK_01353</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PSM-RR</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HMA_HK_01354</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>HMA_HK_01355</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>HMA_HK_01356</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>HMA_HK_01357</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SCU</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HMA_HK_01358</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>HMA_HK_01359</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HMA_HK_01360</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>HMA_HK_01361</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SWRC</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HMA_HK_01362</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>T-CS</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>HMA_HK_01363</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>VCMS</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>HMA_HK_01364</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>VCU</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>HMA_HK_00596</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>VESS</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HMA_HK_01366</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>HMA_HK_01367</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
         <is>
           <t>00</t>
         </is>
